--- a/ResourcesPK/Selling_Category_Bulk_Upload.xlsx
+++ b/ResourcesPK/Selling_Category_Bulk_Upload.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huzaifa\JAR\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" concurrentManualCount="8"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -142,19 +142,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF313131"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -199,17 +193,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -492,320 +483,316 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>50250327</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>50250327</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>50250327</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>50250327</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>50250327</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>50250327</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>50250327</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>50250327</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>50250327</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>50250327</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>50250327</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>50250327</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>50250327</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>50250327</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>50250327</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>50250327</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>50250327</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>50250327</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>50250327</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>50250327</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>50250327</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>50250327</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>50250327</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>50250327</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>50250327</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>50250327</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>50250327</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>50250327</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>50250327</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>50250327</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>50250327</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>50250327</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>50250327</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>50250327</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>50250327</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>50250327</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>50250327</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="1"/>
-      <c r="B39" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ResourcesPK/Selling_Category_Bulk_Upload.xlsx
+++ b/ResourcesPK/Selling_Category_Bulk_Upload.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huzaifa\JAR\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -484,13 +484,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>50250327</v>
       </c>
@@ -506,7 +506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>50250327</v>
       </c>
@@ -514,7 +514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>50250327</v>
       </c>
@@ -522,7 +522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>50250327</v>
       </c>
@@ -530,7 +530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>50250327</v>
       </c>
@@ -538,7 +538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>50250327</v>
       </c>
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>50250327</v>
       </c>
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>50250327</v>
       </c>
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>50250327</v>
       </c>
@@ -570,7 +570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>50250327</v>
       </c>
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>50250327</v>
       </c>
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>50250327</v>
       </c>
@@ -594,7 +594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>50250327</v>
       </c>
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>50250327</v>
       </c>
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>50250327</v>
       </c>
@@ -618,7 +618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>50250327</v>
       </c>
@@ -626,7 +626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>50250327</v>
       </c>
@@ -634,7 +634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>50250327</v>
       </c>
@@ -642,7 +642,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>50250327</v>
       </c>
@@ -650,7 +650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>50250327</v>
       </c>
@@ -658,7 +658,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>50250327</v>
       </c>
@@ -666,7 +666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>50250327</v>
       </c>
@@ -674,7 +674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>50250327</v>
       </c>
@@ -682,7 +682,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>50250327</v>
       </c>
@@ -690,7 +690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>50250327</v>
       </c>
@@ -698,7 +698,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>50250327</v>
       </c>
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>50250327</v>
       </c>
@@ -714,7 +714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>50250327</v>
       </c>
@@ -722,7 +722,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>50250327</v>
       </c>
@@ -730,7 +730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>50250327</v>
       </c>
@@ -738,7 +738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>50250327</v>
       </c>
@@ -746,7 +746,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>50250327</v>
       </c>
@@ -754,7 +754,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>50250327</v>
       </c>
@@ -762,7 +762,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>50250327</v>
       </c>
@@ -770,7 +770,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>50250327</v>
       </c>
@@ -778,7 +778,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>50250327</v>
       </c>
@@ -786,7 +786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>50250327</v>
       </c>
